--- a/storage/app/gtfs/routes.xlsx
+++ b/storage/app/gtfs/routes.xlsx
@@ -1263,7 +1263,7 @@
     <t>Odeon-Westlands-Kangemi-Kinoo-Regen-Kikuyu</t>
   </si>
   <si>
-    <t>hopln</t>
+    <t>navigo</t>
   </si>
 </sst>
 </file>
